--- a/subspaces/04-academic-tutoring/general-education-tutor-agent/agent/QA.xlsx
+++ b/subspaces/04-academic-tutoring/general-education-tutor-agent/agent/QA.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,44 +413,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Sub_Topic</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Source_Reference</t>
+          <t>Display as Suggested Question?
+yes/no</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Định nghĩa đạo hàm theo giới hạn và cách dùng định nghĩa để tìm hệ số góc tiếp tuyến.</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -462,25 +450,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Định nghĩa đạo hàm theo giới hạn và cách dùng định nghĩa để tìm hệ số góc tiếp tuyến.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Đạo hàm của hàm số y = f(x) tại điểm x0 được định nghĩa là: f'(x0) = lim_(h -&gt; 0) [f(x0 + h) - f(x0)] / h (nếu giới hạn này tồn tại hữu hạn). Về mặt hình học, f'(x0) chính là hệ số góc (slope) của tiếp tuyến với đồ thị hàm số tại điểm M(x0, f(x0)). Phương trình tiếp tuyến có dạng: y - f(x0) = f'(x0) * (x - x0).</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Công thức xấp xỉ tuyến tính (Linear Approximation) bằng vi phân và ứng dụng tính gần đúng.</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -492,25 +467,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Công thức xấp xỉ tuyến tính (Linear Approximation) bằng vi phân và ứng dụng tính gần đúng.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Nếu hàm f(x) khả vi tại x = a, phép xấp xỉ tuyến tính (hay đa thức Taylor bậc 1) có dạng: f(x) ≈ L(x) = f(a) + f'(a) * (x - a). Khi x rất gần a, hàm số được xấp xỉ bằng đường tiếp tuyến tại a. Ứng dụng: Tính gần đúng giá trị vô tỉ, ví dụ tính căn bậc hai của 4.02: chọn f(x) = sqrt(x), a = 4, Delta x = 0.02 -&gt; sqrt(4.02) ≈ sqrt(4) + (1 / (2*sqrt(4))) * 0.02 = 2 + 0.005 = 2.005.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Phương pháp tìm bán kính hội tụ R và khoảng hội tụ của chuỗi lũy thừa ∑ a_n * (x - x0)^n.</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -526,29 +488,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Phương pháp tìm bán kính hội tụ R và khoảng hội tụ của chuỗi lũy thừa ∑ a_n * (x - x0)^n.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Áp dụng tiêu chuẩn D'Alembert hoặc Cauchy: Tính L = lim_(n -&gt; ∞) |a_(n+1) / a_n| hoặc L = lim_(n -&gt; ∞) căn bậc n của |a_n|.
-- Nếu L = 0: Chuỗi hội tụ trên toàn trục số, R = ∞.
-- Nếu L = ∞: Chuỗi chỉ hội tụ tại x = x0, R = 0.
-- Nếu 0 &lt; L &lt; ∞: Bán kính hội tụ R = 1 / L.
-Khoảng hội tụ mở là (x0 - R, x0 + R). Sau đó, bắt buộc phải xét riêng sự hội tụ tại hai mút x = x0 - R và x = x0 + R (thay trực tiếp vào chuỗi ban đầu để xét sự hội tụ) nhằm kết luận khoảng hội tụ chuẩn.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tiêu chuẩn Leibniz xét sự hội tụ của chuỗi đan dấu ∑ (-1)^n * b_n (với b_n &gt; 0).</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -563,28 +508,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tiêu chuẩn Leibniz xét sự hội tụ của chuỗi đan dấu ∑ (-1)^n * b_n (với b_n &gt; 0).</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Chuỗi đan dấu ∑ (-1)^n * b_n hội tụ nếu thỏa mãn đồng thời hai điều kiện của tiêu chuẩn Leibniz:
-1. Dãy {b_n} là dãy số giảm dần: b_(n+1) &lt;= b_n với mọi n kể từ một chỉ số N nào đó.
-2. Giới hạn số hạng tổng quát tiến về 0: lim_(n -&gt; ∞) b_n = 0.
-Nếu hội tụ theo Leibniz nhưng chuỗi trị tuyệt đối ∑ b_n phân kỳ, ta gọi chuỗi là Hội tụ bán phần (Conditionally Convergent).</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Quy tắc L'Hopital khử dạng vô định 0/0 và ∞/∞: Điều kiện và những bẫy thường gặp.</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -596,25 +525,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Quy tắc L'Hopital khử dạng vô định 0/0 và ∞/∞: Điều kiện và những bẫy thường gặp.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Định lý: Nếu lim f(x) = lim g(x) = 0 (hoặc cả hai cùng tiến ra ±∞) khi x -&gt; a, và g'(x) khác 0 lân cận a, thì: lim [f(x) / g(x)] = lim [f'(x) / g'(x)] (với điều kiện giới hạn của đạo hàm tồn tại). Bẫy thường gặp: 1) Áp dụng L'Hopital khi biểu thức KHÔNG PHẢI là dạng vô định 0/0 hoặc ∞/∞ (dẫn đến kết quả sai hoàn toàn). 2) Nhầm lẫn giữa đạo hàm của thương f'/g' với đạo hàm phân thức [f/g]'.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Định lý giá trị trung bình Lagrange (Mean Value Theorem) phát biểu thế nào và ý nghĩa hình học?</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -626,25 +542,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Định lý giá trị trung bình Lagrange (Mean Value Theorem) phát biểu thế nào và ý nghĩa hình học?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Nếu f(x) liên tục trên đoạn [a, b] và khả vi trên khoảng (a, b), thì tồn tại ít nhất một điểm c thuộc (a, b) sao cho: f'(c) = [f(b) - f(a)] / (b - a). Ý nghĩa hình học: Trên đồ thị hàm số nối từ A(a, f(a)) đến B(b, f(b)), tồn tại ít nhất một điểm C(c, f(c)) mà tiếp tuyến tại đó song song với cát tuyến nối hai đầu mút AB.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Công thức khai triển Taylor và Maclaurin của một số hàm cơ bản (e^x, sin x, cos x, ln(1+x)).</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -660,29 +563,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Công thức khai triển Taylor và Maclaurin của một số hàm cơ bản (e^x, sin x, cos x, ln(1+x)).</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Khai triển Maclaurin (tại x = 0):
-- e^x = 1 + x + x^2/2! + x^3/3! + ... + x^n/n! + o(x^n)
-- sin(x) = x - x^3/3! + x^5/5! - ... + (-1)^n * x^(2n+1)/(2n+1)! + o(x^(2n+2))
-- cos(x) = 1 - x^2/2! + x^4/4! - ... + (-1)^n * x^(2n)/(2n)! + o(x^(2n+1))
-- ln(1 + x) = x - x^2/2 + x^3/3 - ... + (-1)^(n-1) * x^n/n + o(x^n) (với -1 &lt; x &lt;= 1).</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Phương pháp tích phân từng phần: Công thức và thứ tự ưu tiên đặt u.</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -694,25 +580,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Phương pháp tích phân từng phần: Công thức và thứ tự ưu tiên đặt u.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Công thức: ∫ u dv = u*v - ∫ v du. Thứ tự ưu tiên đặt u kinh điển: 'Nhất Lô (Logarit) - Nhì Đa (Đa thức) - Tam Lượng (Lượng giác) - Tứ Mũ (Hàm mũ)'. Phần còn lại của biểu thức dưới dấu tích phân sẽ được chọn làm dv.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tiêu chuẩn so sánh xác định sự hội tụ của tích phân suy rộng loại 1 (từ a đến vô cùng của f(x) dx).</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -727,28 +600,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tiêu chuẩn so sánh xác định sự hội tụ của tích phân suy rộng loại 1 (từ a đến vô cùng của f(x) dx).</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Cho 0 &lt;= f(x) &lt;= g(x) trên [a, ∞):
-1. Nếu ∫ g(x) dx hội tụ thì ∫ f(x) dx cũng hội tụ.
-2. Nếu ∫ f(x) dx phân kỳ thì ∫ g(x) dx cũng phân kỳ.
-Chuỗi chuẩn so sánh thường dùng là tích phân p-Dirichlet: ∫ (1 / x^p) dx từ 1 đến ∞: Hội tụ khi và chỉ khi p &gt; 1; Phân kỳ khi p &lt;= 1.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Điều kiện để hàm số y = f(x) có cực trị địa phương tại điểm x0 (Dấu hiệu 1 và Dấu hiệu 2).</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -761,26 +618,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Điều kiện để hàm số y = f(x) có cực trị địa phương tại điểm x0 (Dấu hiệu 1 và Dấu hiệu 2).</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>- Dấu hiệu 1: f'(x0) = 0 hoặc f'(x0) không xác định. Nếu f'(x) đổi dấu từ dương sang âm khi qua x0 -&gt; x0 là điểm Cực đại; nếu đổi dấu từ âm sang dương -&gt; x0 là điểm Cực tiểu; nếu không đổi dấu -&gt; không phải cực trị.
-- Dấu hiệu 2: f'(x0) = 0 và f''(x0) tồn tại. Nếu f''(x0) &lt; 0 -&gt; x0 là điểm Cực đại; nếu f''(x0) &gt; 0 -&gt; x0 là điểm Cực tiểu; nếu f''(x0) = 0 -&gt; chưa thể kết luận (phải dùng Dấu hiệu 1 hoặc đạo hàm cấp cao hơn).</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Công thức xác suất toàn phần và công thức Bayes: Ý nghĩa và ví dụ áp dụng trong y tế.</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -791,30 +634,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Công thức xác suất toàn phần và công thức Bayes: Ý nghĩa và ví dụ áp dụng trong y tế.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>- Công thức xác suất toàn phần: Cho hệ biến cố đầy đủ A1, A2,..., An (rời nhau từng đôi và tổng xác suất = 1). Khi đó với biến cố B bất kỳ: P(B) = sum_{i=1}^n P(Ai) * P(B|Ai).
-- Công thức Bayes: Cho phép cập nhật xác suất tiên nghiệm P(Ai) thành xác suất hậu nghiệm P(Ai|B) sau khi đã quan sát thấy biến cố B xảy ra: P(Ai|B) = [P(Ai) * P(B|Ai)] / P(B).
-Ứng dụng y tế: Tính xác suất thực sự mắc bệnh của một bệnh nhân khi que test cho kết quả Dương tính, có tính đến độ nhạy, độ đặc hiệu và tỉ lệ nhiễm bệnh trong cộng đồng.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Phân biệt biến ngẫu nhiên rời rạc và liên tục. Nêu các tính chất của hàm mật độ xác suất f(x).</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -824,29 +652,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Phân biệt biến ngẫu nhiên rời rạc và liên tục. Nêu các tính chất của hàm mật độ xác suất f(x).</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>- Biến ngẫu nhiên rời rạc nhận tập giá trị hữu hạn hoặc đếm được, mô tả bằng Bảng phân phối xác suất và hàm khối PMF: P(X = x_i) = p_i với sum p_i = 1.
-- Biến ngẫu nhiên liên tục nhận giá trị trên một khoảng liên tục, xác suất tại 1 điểm đơn lẻ luôn bằng 0 (P(X = c) = 0), mô tả bằng Hàm mật độ xác suất f(x) thỏa 2 điều kiện: 1) f(x) &gt;= 0 với mọi x; 2) Tích phân từ -∞ đến +∞ của f(x) dx = 1. Xác suất để X rơi vào khoảng [a, b] là: P(a &lt;= X &lt;= b) = ∫_a^b f(x) dx.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Phân phối Chuẩn N(mu, sigma^2): Quy tắc 3-Sigma và cách chuẩn hóa về chuẩn tắc N(0, 1).</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -859,32 +673,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Phân phối Chuẩn N(mu, sigma^2): Quy tắc 3-Sigma và cách chuẩn hóa về chuẩn tắc N(0, 1).</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Biến ngẫu nhiên X ~ N(mu, sigma^2) được chuẩn hóa về biến chuẩn tắc Z ~ N(0, 1) bằng công thức: Z = (X - mu) / sigma. Bảng giá trị hàm Laplace Phi(z) được tra cứu để tính xác suất.
-Quy tắc 3-Sigma (kinh nghiệm thực tế):
-- Khoảng [mu - sigma, mu + sigma] chứa xấp xỉ 68.27% dữ liệu.
-- Khoảng [mu - 2*sigma, mu + 2*sigma] chứa xấp xỉ 95.45% dữ liệu.
-- Khoảng [mu - 3*sigma, mu + 3*sigma] chứa xấp xỉ 99.73% dữ liệu (dữ liệu nằm ngoài khoảng này thường bị coi là điểm ngoại lai / outlier).</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Phân phối Nhị thức B(n, p) và điều kiện xấp xỉ sang phân phối Poisson.</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -897,26 +694,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Phân phối Nhị thức B(n, p) và điều kiện xấp xỉ sang phân phối Poisson.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Phân phối Nhị thức B(n, p) mô tả số lần thành công X trong n phép thử Bernoulli độc lập với xác suất thành công mỗi lần là p: P(X = k) = C_n^k * p^k * (1 - p)^(n - k). Kỳ vọng E(X) = n*p, phương sai Var(X) = n*p*(1 - p).
-Khi số phép thử n rất lớn (n &gt;= 50) và xác suất p rất nhỏ (p &lt;= 0.1) sao cho lambda = n*p là hằng số vừa phải (thường n*p &lt; 10), phân phối Nhị thức được xấp xỉ bằng phân phối Poisson(lambda): P(X = k) ≈ (lambda^k * e^(-lambda)) / k!.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Định lý Giới hạn Trung tâm (Central Limit Theorem - CLT) phát biểu thế nào và tầm quan trọng trong thống kê?</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -928,25 +711,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Định lý Giới hạn Trung tâm (Central Limit Theorem - CLT) phát biểu thế nào và tầm quan trọng trong thống kê?</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLT phát biểu: Cho X1, X2,..., Xn là các biến ngẫu nhiên độc lập cùng phân phối (i.i.d) có kỳ vọng mu và phương sai sigma^2 hữu hạn. Khi kích thước mẫu n đủ lớn (thường n &gt;= 30), biến ngẫu nhiên trung bình mẫu X_bar sẽ có phân phối tiệm cận phân phối Chuẩn: X_bar ~ N(mu, sigma^2 / n) bất kể phân phối gốc của biến ngẫu nhiên ban đầu là gì. Ý nghĩa: Đây là nền tảng toán học cho toàn bộ các phương pháp ước lượng khoảng và kiểm định giả thuyết thống kê trong thực tế.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Các bước tiến hành bài toán Kiểm định giả thuyết thống kê cho kỳ vọng một mẫu (One-sample Test).</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -961,28 +731,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Các bước tiến hành bài toán Kiểm định giả thuyết thống kê cho kỳ vọng một mẫu (One-sample Test).</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1. Đặt giả thuyết: H0: mu = mu0; Đối thuyết H1 (có thể là mu != mu0, mu &gt; mu0, hoặc mu &lt; mu0).
-2. Chọn tiêu chuẩn kiểm định: Nếu đã biết phương sai sigma^2 (hoặc n &gt;= 30), dùng thống kê Z = (X_bar - mu0) / (sigma / sqrt(n)) ~ N(0, 1). Nếu chưa biết phương sai và mẫu nhỏ (n &lt; 30) có phân phối chuẩn, dùng thống kê Student: T = (X_bar - mu0) / (s / sqrt(n)) ~ t(n - 1).
-3. Xác định miền bác bỏ W_alpha dựa vào mức ý nghĩa alpha tra bảng.
-4. Tính giá trị quan sát và kết luận: Nếu giá trị quan sát rơi vào miền W_alpha -&gt; Bác bỏ H0; ngược lại -&gt; Chưa đủ cơ sở bác bỏ H0.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Khoảng tin cậy (Confidence Interval) cho kỳ vọng toán mu khi đã biết phương sai sigma^2.</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -994,25 +748,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Khoảng tin cậy (Confidence Interval) cho kỳ vọng toán mu khi đã biết phương sai sigma^2.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Với độ tin cậy 1 - alpha, khoảng tin cậy đối xứng cho kỳ vọng mu của tổng thể phân phối chuẩn có phương sai sigma^2 đã biết là: (X_bar - z_(alpha/2) * (sigma / sqrt(n)), X_bar + z_(alpha/2) * (sigma / sqrt(n))), trong đó X_bar là trung bình mẫu, n là kích thước mẫu và z_(alpha/2) là giá trị tới hạn chuẩn thỏa mãn Phi(z_(alpha/2)) = (1 - alpha)/2 (ví dụ với độ tin cậy 95%, z_0.025 = 1.96).</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hiệp phương sai (Covariance) và Hệ số tương quan Pearson (Correlation Coefficient) r(X, Y).</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1025,26 +766,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hiệp phương sai (Covariance) và Hệ số tương quan Pearson (Correlation Coefficient) r(X, Y).</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>- Hiệp phương sai: Cov(X, Y) = E[(X - E(X))*(Y - E(Y))] = E(XY) - E(X)*E(Y). Cho biết hướng tương quan (dương là cùng chiều, âm là ngược chiều), nhưng phụ thuộc vào đơn vị đo.
-- Hệ số tương quan Pearson: r(X, Y) = Cov(X, Y) / (sigma_X * sigma_Y). Đại lượng này không phụ thuộc đơn vị đo, luôn nằm trong đoạn [-1, 1]. |r| càng gần 1 thì quan hệ tuyến tính giữa X và Y càng chặt chẽ; r = 0 biểu thị không có quan hệ tuyến tính.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sai lầm loại 1 (Type I Error) và Sai lầm loại 2 (Type II Error) trong kiểm định giả thuyết.</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1057,26 +784,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sai lầm loại 1 (Type I Error) và Sai lầm loại 2 (Type II Error) trong kiểm định giả thuyết.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>- Sai lầm loại 1 (alpha): Bác bỏ giả thuyết H0 khi H0 THỰC SỰ ĐÚNG (kết tội oan người vô tội). Xác suất mắc sai lầm loại 1 chính là Mức ý nghĩa alpha do người nghiên cứu quy định trước (thường là 5% hoặc 1%).
-- Sai lầm loại 2 (beta): Không bác bỏ (chấp nhận) giả thuyết H0 khi H0 THỰC SỰ SAI (bỏ lọt tội phạm). Độ mạnh của kiểm định (Power of test) được tính bằng 1 - beta.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Phương sai mẫu hiệu chỉnh (Sample Variance s^2) tại sao phải chia cho n - 1 thay vì n?</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1088,25 +801,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Phương sai mẫu hiệu chỉnh (Sample Variance s^2) tại sao phải chia cho n - 1 thay vì n?</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Vì công thức chia cho n là một ước lượng bị chệch (Biased Estimator), nó có xu hướng đánh giá thấp phương sai thực tế của tổng thể: E(s_unadjusted^2) = [(n - 1) / n] * sigma^2. Việc chia cho n - 1 (bậc tự do) sẽ khử hoàn toàn độ chệch này, biến s^2 = [1 / (n - 1)] * sum (x_i - x_bar)^2 thành một Ước lượng không chệch (Unbiased Estimator) của phương sai tổng thể sigma^2.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Phương pháp chia đôi (Bisection Method) tìm nghiệm phương trình f(x) = 0: Điều kiện và đánh giá sai số.</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1115,28 +815,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Phương pháp chia đôi (Bisection Method) tìm nghiệm phương trình f(x) = 0: Điều kiện và đánh giá sai số.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Điều kiện: f(x) liên tục trên đoạn [a, b] và thỏa mãn f(a) * f(b) &lt; 0 (định lý Bolzano-Cauchy đảm bảo tồn tại ít nhất 1 nghiệm trong khoảng (a, b)). Thuật toán: Liên tục chia đôi đoạn [a, b] tại điểm giữa c = (a + b) / 2 và thu hẹp đoạn về nửa chứa nghiệm. Đánh giá sai số sau n bước lặp: Sai số tuyệt đối |x_n - x*| &lt;= (b - a) / 2^n. Muốn đạt sai số epsilon, số bước lặp tối thiểu là: n &gt;= log2[(b - a) / epsilon].</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Phương pháp tiếp tuyến Newton-Raphson: Công thức lặp và điều kiện hội tụ bậc hai.</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1145,28 +832,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Phương pháp tiếp tuyến Newton-Raphson: Công thức lặp và điều kiện hội tụ bậc hai.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Công thức lặp: x_(k+1) = x_k - [f(x_k) / f'(x_k)]. Về mặt hình học, x_(k+1) là giao điểm của tiếp tuyến với đồ thị f(x) tại điểm (x_k, f(x_k)) với trục hoành. Điều kiện Fourier đảm bảo hội tụ bậc hai: f(a)*f(b) &lt; 0, f'(x) và f''(x) giữ nguyên dấu không đổi trên [a, b], và chọn điểm xuất phát x0 thỏa mãn f(x0) * f''(x0) &gt; 0. Nhược điểm: Phải tính đạo hàm f'(x) tại mỗi bước lặp và không áp dụng được nếu f'(x_k) ≈ 0.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Đa thức nội suy Lagrange: Công thức tổng quát và ưu/nhược điểm khi bổ sung thêm mốc nội suy.</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1178,25 +852,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Đa thức nội suy Lagrange: Công thức tổng quát và ưu/nhược điểm khi bổ sung thêm mốc nội suy.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Cho n+1 mốc nội suy (x0, y0),..., (xn, yn) phân biệt. Đa thức nội suy Lagrange có dạng: P_n(x) = sum_{i=0}^n y_i * L_i(x), trong đó các đa thức cơ sở L_i(x) = prod_{j != i} [(x - x_j) / (x_i - x_j)]. Ưu điểm: Công thức tường minh, dễ chứng minh tính duy nhất. Nhược điểm chí mạng: Khi bổ sung thêm một mốc nội suy mới (x_(n+1), y_(n+1)), toàn bộ các đa thức cơ sở L_i(x) đều phải tính toán lại từ đầu (tốn kém chi phí, nên trong thực tế người ta ưu tiên dùng Đa thức nội suy Newton).</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Quy tắc hình thang và Quy tắc Simpson 1/3 tính gần đúng tích phân xác định.</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1206,29 +867,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Quy tắc hình thang và Quy tắc Simpson 1/3 tính gần đúng tích phân xác định.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>- Quy tắc Hình thang: Xấp xỉ diện tích hình thang cong bằng diện tích hình thang thẳng: ∫_a^b f(x) dx ≈ [(b - a) / 2] * [f(a) + f(b)]. Công thức mở rộng trên n đoạn: I ≈ (h/2) * [y0 + 2*(y1 + y2 + ... + y_(n-1)) + y_n] với h = (b - a)/n. Sai số cấp O(h^2).
-- Quy tắc Simpson 1/3 (n chẵn): Xấp xỉ hàm số từng khúc bằng parabol bậc hai: I ≈ (h/3) * [y0 + 4*(y1 + y3 + ...) + 2*(y2 + y4 + ...) + y_n]. Sai số cấp O(h^4) (đạt độ chính xác rất cao cho đa thức đến bậc 3).</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Phương pháp lặp Jacobi và Gauss-Seidel giải hệ phương trình tuyến tính Ax = b: Điều kiện ma trận chéo trội.</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1240,25 +887,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Phương pháp lặp Jacobi và Gauss-Seidel giải hệ phương trình tuyến tính Ax = b: Điều kiện ma trận chéo trội.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Biến đổi hệ về dạng x = Bx + d. Jacobi dùng toàn bộ vector nghiệm cũ x^(k) để tính vector nghiệm mới x^(k+1). Gauss-Seidel cải tiến bằng cách dùng ngay các giá trị x_i^(k+1) vừa tính được ở các dòng trên để thế vào các dòng dưới trong cùng một vòng lặp, giúp tốc độ hội tụ nhanh hơn gấp đôi. Điều kiện đủ để các phương pháp lặp này hội tụ với mọi vector xuất phát ban đầu là: Ma trận A là Ma trận chéo trội nghiêm ngặt hàng (|a_ii| &gt; sum_{j != i} |a_ij|) hoặc chéo trội nghiêm ngặt cột.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Phương pháp Runge-Kutta bậc 4 (RK4) giải phương trình vi phân y' = f(x, y) với điều kiện đầu y(x0) = y0.</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1275,30 +909,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Phương pháp Runge-Kutta bậc 4 (RK4) giải phương trình vi phân y' = f(x, y) với điều kiện đầu y(x0) = y0.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Công thức tính giá trị bước kế tiếp y_(n+1) = y_n + (h/6) * (k1 + 2*k2 + 2*k3 + k4), trong đó:
-- k1 = f(x_n, y_n)
-- k2 = f(x_n + h/2, y_n + (h/2)*k1)
-- k3 = f(x_n + h/2, y_n + (h/2)*k2)
-- k4 = f(x_n + h, y_n + h*k3)
-Phương pháp RK4 có sai số cục bộ là O(h^5) và sai số tích lũy toàn cục là O(h^4), đạt độ chính xác rất cao và ổn định, được coi là phương pháp tiêu chuẩn trong tính toán kỹ thuật số.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Phương pháp bình phương bé nhất (Least Squares Method) tìm đường thẳng hồi quy y = ax + b.</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1313,28 +929,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Phương pháp bình phương bé nhất (Least Squares Method) tìm đường thẳng hồi quy y = ax + b.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Mục tiêu: Tìm các tham số a, b sao cho tổng bình phương sai số giữa giá trị thực tế y_i và giá trị dự đoán (a*x_i + b) đạt giá trị cực tiểu: S(a, b) = sum [y_i - (a*x_i + b)]^2 -&gt; min. Bằng cách lấy đạo hàm riêng theo a và b rồi cho bằng 0, ta được Hệ phương trình chuẩn (Normal Equations):
-[sum x_i^2]*a + [sum x_i]*b = sum (x_i * y_i)
-[sum x_i]*a + n*b = sum y_i.
-Giải hệ 2 phương trình bậc nhất này tìm ra hệ số a và b duy nhất.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hiện tượng Runge trong nội suy đa thức bậc cao và giải pháp bằng Nội suy Spline.</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1346,25 +946,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Hiện tượng Runge trong nội suy đa thức bậc cao và giải pháp bằng Nội suy Spline.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Hiện tượng Runge là sự dao động biên độ dữ dội ở hai đầu mút của khoảng nội suy khi sử dụng đa thức nội suy bậc cao với các mốc chia đều (điển hình với hàm f(x) = 1 / (1 + 25*x^2)). Giải pháp khắc phục: 1) Sử dụng các mốc nội suy Chebyshev (các mốc phân bố dày đặc hơn ở hai đầu mút). 2) Dùng Nội suy Spline bậc 3 (Cubic Spline): Chia đoạn thành nhiều đoạn con, trên mỗi đoạn nối bằng một đa thức bậc 3 thỏa mãn tính liên tục trơn tru đến đạo hàm bậc hai tại các nút ghép.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nguyên lý Bù trừ (Inclusion-Exclusion Principle) trong bài toán đếm: Công thức cho 2 và 3 tập hợp.</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1375,30 +962,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nguyên lý Bù trừ (Inclusion-Exclusion Principle) trong bài toán đếm: Công thức cho 2 và 3 tập hợp.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>- Cho 2 tập hợp: |A ∪ B| = |A| + |B| - |A ∩ B|.
-- Cho 3 tập hợp: |A ∪ B ∪ C| = (|A| + |B| + |C|) - (|A ∩ B| + |B ∩ C| + |C ∩ A|) + |A ∩ B ∩ C|.
-- Công thức tổng quát cho n tập hợp: Cộng kích thước từng tập đơn lẻ, trừ đi giao của từng cặp 2 tập, cộng giao của từng bộ 3 tập, trừ giao bộ 4,... và đan dấu (-1)^(k-1) cho giao của k tập hợp.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bài toán chia kẹo của Euler: Số nghiệm nguyên không âm và nguyên dương của x1 + x2 + ... + xk = n.</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1408,29 +980,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bài toán chia kẹo của Euler: Số nghiệm nguyên không âm và nguyên dương của x1 + x2 + ... + xk = n.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>- Số nghiệm nguyên KHÔNG ÂM (x_i &gt;= 0): Tương đương bài toán chia n chiếc kẹo giống nhau cho k đứa trẻ (dùng n viên kẹo và k - 1 thanh ngăn) -&gt; Số cách chọn là: C_(n + k - 1)^(k - 1) hoặc C_(n + k - 1)^n.
-- Số nghiệm NGUYÊN DƯƠNG (x_i &gt;= 1): Mỗi đứa trẻ nhận trước 1 chiếc kẹo, còn lại n - k chiếc kẹo chia tự do (đặt k - 1 vách ngăn vào n - 1 khoảng trống giữa các viên kẹo) -&gt; Số cách chọn là: C_(n - 1)^(k - 1).</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nguyên lý Chuồng bồ câu (Pigeonhole Principle): Dạng cơ bản và dạng mở rộng.</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1440,29 +998,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Nguyên lý Chuồng bồ câu (Pigeonhole Principle): Dạng cơ bản và dạng mở rộng.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>- Dạng cơ bản: Nếu nhốt n + 1 con bồ câu vào n cái chuồng, thì chắc chắn có ít nhất một cái chuồng chứa từ 2 con bồ câu trở lên.
-- Dạng mở rộng: Nếu nhốt N đối tượng vào k hộp, thì chắc chắn tồn tại ít nhất một hộp chứa không ít hơn ceil(N / k) đối tượng (trong đó ceil là hàm làm tròn lên). Ứng dụng: Chứng minh trong một nhóm 367 người luôn có ít nhất 2 người cùng ngày sinh nhật; chứng minh luôn tồn tại 2 người có cùng số sợi tóc trên đầu trong một thành phố.</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dãy số Catalan: Định nghĩa, công thức đóng C_n và các bài toán mô hình tương đương.</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1479,30 +1023,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Dãy số Catalan: Định nghĩa, công thức đóng C_n và các bài toán mô hình tương đương.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Số Catalan thứ n được tính theo công thức đóng: C_n = (1 / (n + 1)) * C_(2n)^n = (2n)! / [(n + 1)! * n!].
-Các bài toán mô hình tương đương kinh điển:
-1. Số cách đặt n cặp dấu ngoặc hợp lệ.
-2. Số cây nhị phân đúng có n + 1 lá (hoặc n nút trong).
-3. Số cách chia một đa giác lồi n + 2 cạnh thành n tam giác bằng các đường chéo không cắt nhau.
-4. Số đường đi Dyck từ (0, 0) đến (2n, 0) không đi xuống dưới trục hoành.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Phương pháp Hàm sinh thông thường (Ordinary Generating Function - OGF) giải bài toán đếm tổ hợp.</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1514,25 +1040,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Phương pháp Hàm sinh thông thường (Ordinary Generating Function - OGF) giải bài toán đếm tổ hợp.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Hàm sinh thông thường của dãy số {a_n} là chuỗi lũy thừa hình thức: G(x) = sum_{n=0}^∞ a_n * x^n. Phép nhân hai hàm sinh tương ứng với tích chập của hai dãy số. Ứng dụng: Để tìm số cách chọn n vật thỏa mãn các ràng buộc (ví dụ: vật loại 1 chọn từ 1 đến 3 cái, vật loại 2 chọn chẵn cái), ta biểu diễn mỗi ràng buộc thành một đa thức theo biến x, nhân các đa thức lại với nhau, và hệ số của x^n trong biểu thức tích chính là số cách chọn cần tìm.</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hệ thức truy hồi tuyến tính thuần nhất bậc 2 hệ số hằng: a_n = c1*a_(n-1) + c2*a_(n-2).</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1548,29 +1061,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hệ thức truy hồi tuyến tính thuần nhất bậc 2 hệ số hằng: a_n = c1*a_(n-1) + c2*a_(n-2).</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Xét phương trình đặc trưng: r^2 - c1*r - c2 = 0.
-- Trường hợp 1 (Hai nghiệm thực phân biệt r1 != r2): Nghiệm tổng quát có dạng a_n = A * (r1)^n + B * (r2)^n.
-- Trường hợp 2 (Nghiệm kép r1 = r2 = r0): Nghiệm tổng quát có dạng a_n = (A + B*n) * (r0)^n.
-- Trường hợp 3 (Hai nghiệm phức liên hợp r = rho * e^(± i*theta)): Nghiệm tổng quát dạng a_n = rho^n * [A * cos(n*theta) + B * sin(n*theta)].
-Các hằng số A, B được xác định từ hai điều kiện ban đầu a0 và a1.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Số Stirling loại hai S(n, k) đại diện cho bài toán phân hoạch nào?</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1582,25 +1078,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Số Stirling loại hai S(n, k) đại diện cho bài toán phân hoạch nào?</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>S(n, k) là số cách phân hoạch một tập hợp gồm n phần tử phân biệt thành k tập con khác rỗng không phân biệt (tương đương bài toán xếp n quả bóng khác nhau vào k chiếc hộp giống hệt nhau sao cho không có hộp nào rỗng). Hệ thức truy hồi: S(n, k) = S(n - 1, k - 1) + k * S(n - 1, k) với điều kiện biên S(n, 1) = S(n, n) = 1 và S(n, k) = 0 khi k &gt; n.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Định lý Kronecker-Capelli xác định số nghiệm của hệ phương trình tuyến tính Ax = b.</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1613,32 +1096,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Định lý Kronecker-Capelli xác định số nghiệm của hệ phương trình tuyến tính Ax = b.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Gọi A là ma trận hệ số và (A|b) là ma trận mở rộng. Định lý phát biểu:
-1. Hệ có nghiệm khi và chỉ khi hạng của ma trận hệ số bằng hạng của ma trận mở rộng: rank(A) = rank(A|b).
-2. Nếu rank(A) = rank(A|b) = n (số ẩn): Hệ có nghiệm DUY NHẤT.
-3. Nếu rank(A) = rank(A|b) = r &lt; n: Hệ có VÔ SỐ NGHIỆM phụ thuộc vào n - r tham số tự do.
-4. Nếu rank(A) &lt; rank(A|b): Hệ VÔ NGHIỆM.</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Điều kiện để ma trận vuông A khả nghịch và công thức tìm ma trận nghịch đảo qua ma trận phụ hợp.</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1647,28 +1113,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Điều kiện để ma trận vuông A khả nghịch và công thức tìm ma trận nghịch đảo qua ma trận phụ hợp.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Ma trận vuông A cấp n khả nghịch khi và chỉ khi định thức của nó khác không: det(A) != 0. Khi đó công thức tính ma trận nghịch đảo là: A^(-1) = (1 / det(A)) * adj(A) = (1 / det(A)) * C^T, trong đó adj(A) là ma trận phụ hợp, chính là chuyển vị của ma trận các phần bù đại số C_ij = (-1)^(i + j) * det(M_ij), với M_ij là ma trận con bỏ đi dòng i và cột j.</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Khái niệm Hệ vector độc lập tuyến tính, Phụ thuộc tuyến tính và cách kiểm tra bằng Hạng ma trận.</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1677,28 +1130,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Khái niệm Hệ vector độc lập tuyến tính, Phụ thuộc tuyến tính và cách kiểm tra bằng Hạng ma trận.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Tập vector {v1, v2,..., vk} độc lập tuyến tính nếu phương trình vector c1*v1 + c2*v2 + ... + ck*vk = 0 CHỈ CÓ nghiệm tầm thường c1 = c2 = ... = ck = 0. Nếu tồn tại bộ số không đồng thời bằng 0 thỏa phương trình thì tập là phụ thuộc tuyến tính. Cách kiểm tra: Xếp các vector thành các dòng của ma trận A, dùng phép biến đổi sơ cấp đưa về ma trận bậc thang: Nếu rank(A) = k thì hệ độc lập tuyến tính; nếu rank(A) &lt; k thì hệ phụ thuộc tuyến tính.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Định lý về Hạng và Số chiều nhân (Rank-Nullity Theorem) của ánh xạ tuyến tính T: V -&gt; W.</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1710,25 +1150,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Định lý về Hạng và Số chiều nhân (Rank-Nullity Theorem) của ánh xạ tuyến tính T: V -&gt; W.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Cho T là ánh xạ tuyến tính từ không gian vector V (hữu hạn chiều) vào không gian vector W. Định lý phát biểu: dim(V) = dim(Ker(T)) + dim(Im(T)) = nullity(T) + rank(T). Ý nghĩa: Tổng số chiều của hạt nhân (Kernel - tập các vector biến thành vector 0) và số chiều của ảnh (Image - không gian sinh bởi các vector đầu ra) luôn bằng đúng số chiều của không gian nguồn V.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Quy trình trực chuẩn hóa Gram-Schmidt biến đổi một cơ sở bất kỳ thành cơ sở trực chuẩn.</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1744,29 +1171,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Quy trình trực chuẩn hóa Gram-Schmidt biến đổi một cơ sở bất kỳ thành cơ sở trực chuẩn.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Cho cơ sở {v1, v2,..., vk} của không gian Euclid:
-1. u1 = v1, e1 = u1 / ||u1||.
-2. u2 = v2 - proj_u1(v2) = v2 - [(&lt;v2, u1&gt; / ||u1||^2) * u1], e2 = u2 / ||u2||.
-3. Tổng quát: u_i = v_i - sum_{j=1}^{i-1} [(&lt;v_i, u_j&gt; / ||u_j||^2) * u_j], sau đó trực chuẩn hóa: e_i = u_i / ||u_i||.
-Tập {e1, e2,..., ek} thu được là một cơ sở trực chuẩn (đôi một trực giao và có độ dài bằng 1).</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Các bước chéo hóa ma trận vuông A cấp n (Diagonalization) và điều kiện để A chéo hóa được.</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1778,31 +1188,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Các bước chéo hóa ma trận vuông A cấp n (Diagonalization) và điều kiện để A chéo hóa được.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Điều kiện cần và đủ: Ma trận A cấp n chéo hóa được khi và chỉ khi A có đủ n vector riêng độc lập tuyến tính. Các bước thực hiện:
-1. Giải phương trình đặc trưng det(A - lambda*I) = 0 để tìm các trị riêng lambda_i.
-2. Với mỗi trị riêng, giải hệ (A - lambda_i*I)x = 0 để tìm các vector riêng độc lập tuyến tính tương ứng.
-3. Nếu tổng số vector riêng tìm được = n, đặt ma trận làm chéo P = [v1 | v2 | ... | vn] và ma trận đường chéo D = diag(lambda1, ..., lambdan). Khi đó: A = P * D * P^(-1).</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Định lý Phổ (Spectral Theorem) cho ma trận đối xứng thực A = A^T.</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1814,25 +1208,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Định lý Phổ (Spectral Theorem) cho ma trận đối xứng thực A = A^T.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Định lý Phổ phát biểu: Mọi ma trận đối xứng thực A đều chéo hóa trực giao được. Nghĩa là: 1) Tất cả các trị riêng của A đều là số thực. 2) Các vector riêng ứng với các trị riêng phân biệt thì đôi một trực giao với nhau. 3) Luôn tồn tại một Ma trận trực giao P (thỏa P^(-1) = P^T) sao cho P^T * A * P = D là ma trận đường chéo.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ý nghĩa hình học của Định thức det(A) trong không gian R^2 và R^3.</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1845,110 +1226,55 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Ý nghĩa hình học của Định thức det(A) trong không gian R^2 và R^3.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>- Trong R^2: Giá trị tuyệt đối |det([v1 | v2])| biểu diễn Diện tích của hình bình hành tạo bởi hai vector v1 và v2.
-- Trong R^3: Giá trị tuyệt đối |det([v1 | v2 | v3])| biểu diễn Thể tích của khối hộp hình bình hành tạo bởi ba vector v1, v2, v3. Dấu của định thức cho biết định hướng của hệ tọa độ (thuận hay nghịch chiều kim đồng hồ theo quy tắc bàn tay phải).</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bạn có biết các Agent khác trong hệ sinh thái HCMUS Smart Campus không?</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Tôi là Trợ giảng Đại cương (General Education Tutor Agent) thuộc tầng 1 trong Sub-space 4. Tôi phối hợp chặt chẽ với: Political Theory Tutor Agent (Tầng 2 - Chính trị), Core Foundations Tutor Agent (Tầng 3 - Cơ sở ngành), Specialized Major Tutor Agent (Tầng 4 - Chuyên ngành) và Library Research Agent ở Sub-space 2.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Bạn có biết các Agent khác trong hệ sinh thái HCMUS Smart Campus không?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Tôi là Trợ giảng Đại cương (General Education Tutor Agent) thuộc tầng 1 trong Sub-space 4. Tôi phối hợp chặt chẽ với: Political Theory Tutor Agent (Tầng 2 - Chính trị), Core Foundations Tutor Agent (Tầng 3 - Cơ sở ngành), Specialized Major Tutor Agent (Tầng 4 - Chuyên ngành) và Library Research Agent ở Sub-space 2.</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Môn Giải tích 1 và Giải tích 2 có những nội dung nào trọng tâm?</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Giải tích 1 tập trung vào giới hạn, đạo hàm, khảo sát hàm số, tích phân suy rộng và chuỗi số. Giải tích 2 mở rộng sang không gian đa chiều: hàm nhiều biến, cực trị tự do/có điều kiện Lagrange, tích phân kép, tích phân bội ba, tích phân đường và tích phân mặt.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Môn Giải tích 1 và Giải tích 2 có những nội dung nào trọng tâm?</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Giải tích 1 tập trung vào giới hạn, đạo hàm, khảo sát hàm số, tích phân suy rộng và chuỗi số. Giải tích 2 mở rộng sang không gian đa chiều: hàm nhiều biến, cực trị tự do/có điều kiện Lagrange, tích phân kép, tích phân bội ba, tích phân đường và tích phân mặt.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Làm thế nào để học tốt môn Đại số tuyến tính?</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Bạn cần nắm vững phương pháp khử Gauss để giải hệ phương trình, hiểu bản chất không gian vector, tính độc lập tuyến tính, cơ sở và số chiều. Đặc biệt rèn luyện kỹ thuật tìm trị riêng, vector riêng và chéo hóa ma trận vì đây là câu hỏi chiếm điểm cao trong đề thi cuối kỳ.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Làm thế nào để học tốt môn Đại số tuyến tính?</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Bạn cần nắm vững phương pháp khử Gauss để giải hệ phương trình, hiểu bản chất không gian vector, tính độc lập tuyến tính, cơ sở và số chiều. Đặc biệt rèn luyện kỹ thuật tìm trị riêng, vector riêng và chéo hóa ma trận vì đây là câu hỏi chiếm điểm cao trong đề thi cuối kỳ.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
